--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclipse\Desktop\Automation-Testing-2025\Eclipse\Automation\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF4D4BC-4079-443E-9612-5FF04E3425D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4584F-F0AA-49AF-8723-FC54DB24C118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -607,7 +607,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>345690</v>
+        <v>345699</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -616,13 +616,13 @@
         <v>1000421</v>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F2" s="5">
-        <v>110001023578</v>
+        <v>110001029302</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
@@ -634,7 +634,7 @@
         <v>9</v>
       </c>
       <c r="J2" s="10">
-        <v>100001</v>
+        <v>100006</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -859,20 +859,20 @@
         <v>100673000000011</v>
       </c>
       <c r="B2" s="10">
-        <v>2657</v>
+        <v>2726</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
         <v>0</v>
       </c>
       <c r="E2" s="10">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F2" s="10">
         <v>100</v>
       </c>
       <c r="G2" s="10">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4584F-F0AA-49AF-8723-FC54DB24C118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F386FA-CF9F-40AD-BE52-7C7EFFEFDEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -607,7 +607,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>345699</v>
+        <v>345700</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -622,7 +622,7 @@
         <v>182116420000014</v>
       </c>
       <c r="F2" s="5">
-        <v>110001029302</v>
+        <v>110001029344</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
@@ -859,20 +859,20 @@
         <v>100673000000011</v>
       </c>
       <c r="B2" s="10">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
         <v>0</v>
       </c>
       <c r="E2" s="10">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="F2" s="10">
         <v>100</v>
       </c>
       <c r="G2" s="10">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F386FA-CF9F-40AD-BE52-7C7EFFEFDEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A0343F-3FB6-4680-B779-83FEB774EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>pledge_Req_Number</t>
   </si>
@@ -91,13 +91,16 @@
   </si>
   <si>
     <t>pledge_Cls_Confrim_Req_No</t>
+  </si>
+  <si>
+    <t>SBIN0015088</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,13 +163,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -209,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -226,6 +241,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE2D4B77-1528-40FA-B451-DA61A4400042}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -607,10 +625,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
-        <v>345700</v>
+        <v>345702</v>
       </c>
       <c r="B2" s="5">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="C2" s="4">
         <v>1000421</v>
@@ -619,22 +637,22 @@
         <v>15</v>
       </c>
       <c r="E2" s="5">
-        <v>182116420000014</v>
+        <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001029344</v>
+        <v>110001034831</v>
       </c>
       <c r="G2" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H2" s="4">
         <v>100000</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>100006</v>
+        <v>100007</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -766,45 +784,43 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F7" s="13">
-        <v>110001023776</v>
-      </c>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="14">
-        <v>110001023792</v>
-      </c>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F9" s="14">
-        <v>110001023818</v>
-      </c>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F10" s="14">
-        <v>110001023834</v>
-      </c>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F11" s="14">
-        <v>110001023859</v>
-      </c>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F12" s="14">
-        <v>110001023875</v>
-      </c>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="14">
-        <v>110001023891</v>
-      </c>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F15" s="13"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E16" s="1"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E17" s="1"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -856,23 +872,23 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="B2" s="10">
-        <v>2727</v>
+        <v>2824</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
         <v>0</v>
       </c>
       <c r="E2" s="10">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="F2" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G2" s="10">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A0343F-3FB6-4680-B779-83FEB774EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F897BA5-08AD-4786-9BBE-89A03510ADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -179,7 +179,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -241,9 +241,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,13 +667,13 @@
         <v>1000421</v>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F3" s="11">
-        <v>110001023594</v>
+        <v>110001033668</v>
       </c>
       <c r="G3" s="4">
         <v>100</v>
@@ -684,7 +685,7 @@
         <v>9</v>
       </c>
       <c r="J3" s="10">
-        <v>100002</v>
+        <v>110002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -698,16 +699,16 @@
         <v>1000421</v>
       </c>
       <c r="D4" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E4" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F4" s="12">
-        <v>110001023610</v>
+        <v>110001033643</v>
       </c>
       <c r="G4" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H4" s="4">
         <v>100000</v>
@@ -716,7 +717,7 @@
         <v>9</v>
       </c>
       <c r="J4" s="10">
-        <v>100003</v>
+        <v>100008</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -730,16 +731,16 @@
         <v>1000421</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F5" s="12">
-        <v>110001023651</v>
+        <v>110001033585</v>
       </c>
       <c r="G5" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4">
         <v>100000</v>
@@ -762,16 +763,16 @@
         <v>1000421</v>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F6" s="12">
-        <v>110001023677</v>
+        <v>110001033569</v>
       </c>
       <c r="G6" s="4">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H6" s="4">
         <v>100000</v>
@@ -813,14 +814,14 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E16" s="1"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="1"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="18"/>
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E17" s="1"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F897BA5-08AD-4786-9BBE-89A03510ADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF19571-302C-4773-85A9-C06079F8452F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -241,10 +241,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,14 +813,10 @@
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E16" s="18"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E17" s="18"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="18"/>
+      <c r="F16" s="18"/>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -873,23 +868,23 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>120733340001420</v>
+        <v>100673000000011</v>
       </c>
       <c r="B2" s="10">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
         <v>0</v>
       </c>
       <c r="E2" s="10">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="F2" s="10">
         <v>50</v>
       </c>
       <c r="G2" s="10">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF19571-302C-4773-85A9-C06079F8452F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9036B0-9ECD-4798-AD27-A9A87F183DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -868,23 +868,23 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="B2" s="10">
-        <v>2826</v>
+        <v>2683</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E2" s="10">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F2" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G2" s="10">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9036B0-9ECD-4798-AD27-A9A87F183DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDFA654-C17E-4E96-9BBA-B833B2BDD301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -753,7 +753,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>345694</v>
+        <v>345675</v>
       </c>
       <c r="B6" s="5">
         <v>100673000000011</v>
@@ -762,16 +762,16 @@
         <v>1000421</v>
       </c>
       <c r="D6" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E6" s="5">
         <v>182116420000014</v>
       </c>
       <c r="F6" s="12">
-        <v>110001033569</v>
+        <v>110001036182</v>
       </c>
       <c r="G6" s="4">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H6" s="4">
         <v>100000</v>
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
       <c r="J6" s="10">
-        <v>100005</v>
+        <v>100011</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -868,23 +868,23 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>120733340001420</v>
+        <v>182116420000014</v>
       </c>
       <c r="B2" s="10">
-        <v>2683</v>
+        <v>2867</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E2" s="10">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F2" s="10">
         <v>100</v>
       </c>
       <c r="G2" s="10">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDFA654-C17E-4E96-9BBA-B833B2BDD301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422BC8B1-FB2C-4923-A507-D76EFDF37375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422BC8B1-FB2C-4923-A507-D76EFDF37375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A29106-3166-4343-8634-340D48EF3BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A29106-3166-4343-8634-340D48EF3BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FF8825-360B-4F60-8405-E5B7B6E131FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FF8825-360B-4F60-8405-E5B7B6E131FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C7DD6-FCA0-4908-BE6E-9101B63109C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -244,6 +244,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,8 +625,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>345702</v>
+      <c r="A2" s="5">
+        <v>142085216067</v>
       </c>
       <c r="B2" s="5">
         <v>120733340001420</v>
@@ -640,10 +641,10 @@
         <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001034831</v>
+        <v>110001039418</v>
       </c>
       <c r="G2" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4">
         <v>100000</v>
@@ -652,7 +653,7 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>100007</v>
+        <v>100014</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -784,13 +785,13 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F7" s="13"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="14"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F9" s="14"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F10" s="14"/>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C7DD6-FCA0-4908-BE6E-9101B63109C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE911BD0-7076-495E-9A02-84E0C825FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>pledge_Req_Number</t>
   </si>
@@ -94,13 +94,22 @@
   </si>
   <si>
     <t>SBIN0015088</t>
+  </si>
+  <si>
+    <t>Non_Agricultural</t>
+  </si>
+  <si>
+    <t>Commodity_Segment</t>
+  </si>
+  <si>
+    <t>170420271C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +177,12 @@
       <color rgb="FF2A314A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -224,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -245,6 +260,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE2D4B77-1528-40FA-B451-DA61A4400042}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -590,9 +606,10 @@
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="9" width="18.5703125" customWidth="1"/>
     <col min="10" max="10" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -623,40 +640,46 @@
       <c r="J1" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>142085216067</v>
+        <v>170420267</v>
       </c>
       <c r="B2" s="5">
-        <v>120733340001420</v>
+        <v>100673000000011</v>
       </c>
       <c r="C2" s="4">
         <v>1000421</v>
       </c>
       <c r="D2" s="4">
-        <v>15</v>
+        <v>1003</v>
       </c>
       <c r="E2" s="5">
         <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001039418</v>
+        <v>110001048690</v>
       </c>
       <c r="G2" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="10">
-        <v>100014</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>345691</v>
       </c>
@@ -687,8 +710,9 @@
       <c r="J3" s="10">
         <v>110002</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>345692</v>
       </c>
@@ -719,8 +743,9 @@
       <c r="J4" s="10">
         <v>100008</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>345693</v>
       </c>
@@ -751,8 +776,9 @@
       <c r="J5" s="10">
         <v>100004</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>345675</v>
       </c>
@@ -783,37 +809,38 @@
       <c r="J6" s="10">
         <v>100011</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F9" s="19"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F10" s="14"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F12" s="14"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F13" s="14"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F14" s="13"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E15" s="16"/>
       <c r="F15" s="17"/>
       <c r="G15" s="16"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="6:6" x14ac:dyDescent="0.25">

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE911BD0-7076-495E-9A02-84E0C825FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9AD0D1-747E-400C-9DF3-E63E1EC22F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>pledge_Req_Number</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Commodity_Segment</t>
-  </si>
-  <si>
-    <t>170420271C</t>
   </si>
 </sst>
 </file>
@@ -239,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -261,6 +258,7 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,7 +644,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>170420267</v>
+        <v>210420277</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -672,8 +670,8 @@
       <c r="I2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>21</v>
+      <c r="J2" s="10">
+        <v>210420261</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>19</v>
@@ -812,10 +810,10 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F7" s="5"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F8" s="5"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F9" s="19"/>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9AD0D1-747E-400C-9DF3-E63E1EC22F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D1071B-6E83-4BB6-9DCF-BBE2112679DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -644,7 +644,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>210420277</v>
+        <v>220420282</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -659,7 +659,7 @@
         <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001048690</v>
+        <v>110001048716</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>210420261</v>
+        <v>220420261</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>19</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D1071B-6E83-4BB6-9DCF-BBE2112679DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F61F32-F9E8-40DE-9C26-255A8EEE5B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
   <sheets>
     <sheet name="PladgeRequest" sheetId="1" r:id="rId1"/>
@@ -644,7 +644,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>220420282</v>
+        <v>208420261</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -659,7 +659,7 @@
         <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001048716</v>
+        <v>110001048435</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>220420261</v>
+        <v>280420261</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>19</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F61F32-F9E8-40DE-9C26-255A8EEE5B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EAE9B2-6549-4182-9465-D7472B9FAD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -644,7 +644,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>208420261</v>
+        <v>290420261</v>
       </c>
       <c r="B2" s="5">
         <v>100673000000011</v>
@@ -659,7 +659,7 @@
         <v>181818180000016</v>
       </c>
       <c r="F2" s="5">
-        <v>110001048435</v>
+        <v>110001048492</v>
       </c>
       <c r="G2" s="4">
         <v>1</v>
@@ -671,7 +671,7 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>280420261</v>
+        <v>290420261</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>19</v>
@@ -894,23 +894,23 @@
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <v>182116420000014</v>
+        <v>100673000000011</v>
       </c>
       <c r="B2" s="10">
-        <v>2867</v>
+        <v>3187</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="10">
+        <v>1003</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1001</v>
+      </c>
+      <c r="F2" s="10">
         <v>1</v>
       </c>
-      <c r="E2" s="10">
-        <v>1225</v>
-      </c>
-      <c r="F2" s="10">
-        <v>100</v>
-      </c>
       <c r="G2" s="10">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H2" s="10">
         <v>100000</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EAE9B2-6549-4182-9465-D7472B9FAD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35FDA99-E208-4ABF-8ABB-B8CE868DF065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -96,10 +96,10 @@
     <t>SBIN0015088</t>
   </si>
   <si>
-    <t>Non_Agricultural</t>
-  </si>
-  <si>
     <t>Commodity_Segment</t>
+  </si>
+  <si>
+    <t>Agricultural</t>
   </si>
 </sst>
 </file>
@@ -639,30 +639,30 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>290420261</v>
+        <v>60520261</v>
       </c>
       <c r="B2" s="5">
-        <v>100673000000011</v>
+        <v>120484000000134</v>
       </c>
       <c r="C2" s="4">
-        <v>1000421</v>
+        <v>6539191</v>
       </c>
       <c r="D2" s="4">
-        <v>1003</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5">
-        <v>181818180000016</v>
-      </c>
-      <c r="F2" s="5">
-        <v>110001048492</v>
+        <v>130275000000019</v>
+      </c>
+      <c r="F2" s="18">
+        <v>110001503124</v>
       </c>
       <c r="G2" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4">
         <v>1000</v>
@@ -671,10 +671,10 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>290420261</v>
+        <v>60520261</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35FDA99-E208-4ABF-8ABB-B8CE868DF065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7C67AB-81B5-4F00-9884-DB1EFE40EA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -644,7 +644,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>60520261</v>
+        <v>180520263</v>
       </c>
       <c r="B2" s="5">
         <v>120484000000134</v>
@@ -659,7 +659,7 @@
         <v>130275000000019</v>
       </c>
       <c r="F2" s="18">
-        <v>110001503124</v>
+        <v>110001509204</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
@@ -671,15 +671,15 @@
         <v>18</v>
       </c>
       <c r="J2" s="10">
-        <v>60520261</v>
+        <v>180520261</v>
       </c>
       <c r="K2" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>345691</v>
+      <c r="A3" s="5">
+        <v>180520261</v>
       </c>
       <c r="B3" s="5">
         <v>100673000000011</v>

--- a/Data/PlageData.xlsx
+++ b/Data/PlageData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7C67AB-81B5-4F00-9884-DB1EFE40EA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468ED902-0574-4A6C-9EA4-A1B01B141E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{4E1EDA3E-BBF6-4E09-A300-A7AE4A5B2705}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>pledge_Req_Number</t>
   </si>
@@ -93,20 +93,14 @@
     <t>pledge_Cls_Confrim_Req_No</t>
   </si>
   <si>
-    <t>SBIN0015088</t>
-  </si>
-  <si>
     <t>Commodity_Segment</t>
-  </si>
-  <si>
-    <t>Agricultural</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,12 +169,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -236,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -257,7 +245,6 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -639,12 +626,12 @@
         <v>10</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>180520263</v>
+        <v>10620262</v>
       </c>
       <c r="B2" s="5">
         <v>120484000000134</v>
@@ -655,27 +642,25 @@
       <c r="D2" s="4">
         <v>15</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="11">
         <v>130275000000019</v>
       </c>
-      <c r="F2" s="18">
-        <v>110001509204</v>
+      <c r="F2" s="11">
+        <v>110001509865</v>
       </c>
       <c r="G2" s="4">
         <v>100</v>
       </c>
       <c r="H2" s="4">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="10">
-        <v>180520261</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>20</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J2" s="5">
+        <v>10620262</v>
+      </c>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
@@ -810,10 +795,10 @@
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F7" s="21"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F8" s="21"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F9" s="19"/>
